--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Передача сведений в ГИС" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Примечания" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$I$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -63,12 +64,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -436,19 +440,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -474,36 +477,31 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Документ СУОТ</t>
+          <t>ГИС</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ГИС</t>
+          <t>Сведения, подлежащие передачи</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Какие сведения передаются</t>
+          <t>Участник передачи</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Участник передачи</t>
+          <t>Роль участника</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Роль участника</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
           <t>Вид документа</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -514,46 +512,41 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ч. 6 ст. 8 Федерального закона № 426-ФЗ; п. 3 Методики проведения СОУТ (прил. № 1 к приказу № 817н)</t>
+          <t>ч. 6 ст. 8 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Сведения для присвоения идентификационного номера предстоящей СОУТ / уведомление работодателю об идентификационном номере</t>
+          <t>ФГИС учета результатов проведения специальной оценки условий труда (ФГИС СОУТ)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ФГИС учета результатов проведения СОУТ (ФГИС СОУТ)</t>
+          <t>Сведения в отношении работодателя: полное наименование; идентификационный номер налогоплательщика; код причины постановки на учет в налоговом органе (пп. «а», «в», «в.1» п. 1 ч. 2 ст. 18 Федерального закона № 426-ФЗ) — для присвоения идентификационного номера предстоящей СОУТ</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>В отношении работодателя: полное наименование; ИНН; КПП (пп. «а», «в», «в.1» п. 1 ч. 2 ст. 18); получение идентификационного номера СОУТ, присваиваемого ФГИС СОУТ в автоматическом режиме</t>
+          <t>Организация, проводящая специальную оценку условий труда</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Организация, проводящая СОУТ</t>
+          <t>Передача сведений в информационную систему учета (до начала работ по СОУТ, но не позднее 5 рабочих дней со дня заключения договора)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Передача сведений в ФГИС СОУТ; получение идентификационного номера; сообщение номера работодателю до начала работ (не позднее 5 рабочих дней со дня заключения договора)</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Электронный документ (передача в ФГИС СОУТ); уведомление работодателю — на бумажном носителе / заказным почтовым отправлением / лично либо электронный документ, подписанный УКЭП</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="90" customHeight="1">
+          <t>Электронный документ (передача в ФГИС СОУТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -564,46 +557,41 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ч. 6 ст. 8 Федерального закона № 426-ФЗ; п. 3 Методики проведения СОУТ (прил. № 1 к приказу № 817н)</t>
+          <t>ч. 1, 2, 3 ст. 18 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Уведомление о получении идентификационного номера предстоящей СОУТ</t>
+          <t>ФГИС СОУТ</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ФГИС СОУТ (источник присвоения номера)</t>
+          <t>Сведения о результатах проведения СОУТ (объекты учета по ч. 2 ст. 18), в том числе в отношении рабочих мест, условия труда на которых декларируются: 1) о работодателе — полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда; 2) о рабочем месте — индивидуальный номер РМ; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда и по каждому вредному/опасному фактору (наименование, единицы измерения, измеренные значения, нормативы, продолжительность воздействия, сведения о снижении класса/подкласса с учетом СИЗ); основание прав на досрочную страховую пенсию по старости (при наличии); сведения о НС на производстве и профзаболеваниях за последние 5 лет; сведения о качестве результатов СОУТ; сведения о решении о прекращении действия декларации; 3) об организации, проводившей СОУТ — полное наименование; регистрационный номер в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах; сведения о средствах измерений; сведения, предусмотренные ч. 1.1 ст. 19. За исключением сведений, составляющих государственную или иную охраняемую законом тайну, с учетом требований о персональных данных</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Идентификационный номер предстоящей СОУТ</t>
+          <t>Организация, проводящая специальную оценку условий труда</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Работодатель</t>
+          <t>Передача сведений в информационную систему учета в течение 10 рабочих дней со дня утверждения отчета о проведении СОУТ; подписание УКЭП</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Получение уведомления (до начала работ по СОУТ)</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Бумага / электронный документ с УКЭП</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="90" customHeight="1">
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -614,46 +602,41 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ч. 1, 2, 3 ст. 18 Федерального закона № 426-ФЗ; п. 107 Методики (прил. № 1 к приказу № 817н) — идентификационный номер на титульном листе отчета</t>
+          <t>ч. 4, 5 ст. 18 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении специальной оценки условий труда (сведения о результатах СОУТ)</t>
+          <t>ФГИС СОУТ</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ФГИС СОУТ</t>
+          <t>Сведения в отношении объектов учета, указанных в ч. 2 ст. 18 Федерального закона № 426-ФЗ (в случае невыполнения организацией, проводящей СОУТ, обязанностей по ч. 1 и 3 ст. 18)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Объекты учета по ч. 2 ст. 18: сведения о работодателе (наименование, место нахождения/деятельности, ИНН, КПП, ОГРН, ОКВЭД, количество РМ, количество РМ с СОУТ, распределение по классам/подклассам); о рабочем месте (индивидуальный номер РМ, код профессии, СНИЛС, численность, класс/подкласс и факторы, основание досрочной пенсии, НС и профзаболевания за 5 лет, качество результатов СОУТ, сведения о прекращении действия декларации); об организации, проводившей СОУТ (наименование, рег. номер в реестре, ИНН, ОГРН, аккредитация ИЛ, эксперты, средства измерений, сведения по ч. 1.1 ст. 19), в т.ч. по декларируемым РМ; за исключением гостайны и с учетом персональных данных</t>
+          <t>Территориальный орган Роструда (государственная инспекция труда)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Организация, проводящая СОУТ</t>
+          <t>Передача сведений в информационную систему учета в форме электронного документа, подписанного УКЭП (на основании сведений, представленных работодателем в территориальный орган)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Передача сведений в ФГИС СОУТ в течение 10 рабочих дней со дня утверждения отчета; подписание УКЭП</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Электронный документ, подписанный УКЭП</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="90" customHeight="1">
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -664,46 +647,41 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ч. 3 ст. 18 Федерального закона № 426-ФЗ</t>
+          <t>ч. 1–3 ст. 11 Федерального закона № 426-ФЗ; п. 2–4 Порядка подачи декларации (прил. № 2 к приказу № 406н); п. 1, 3, 4, 6 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Уведомление работодателя о внесении сведений в ФГИС СОУТ; копии подтверждающих документов; сведения, переданные в ФГИС СОУТ</t>
+          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда (формирование и ведение — Роструд и его территориальные органы)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>ФГИС СОУТ</t>
+          <t>Сведения о декларации, подлежащие внесению в реестр (п. 6 Порядка формирования и ведения реестра): полное наименование ЮЛ (ФИО ИП); место нахождения и место осуществления деятельности; ИНН; ОГРН; полное наименование организации, проводившей СОУТ; перечень рабочих мест (индивидуальный номер РМ, численность работников); реквизиты заключения эксперта и (или) протокола (протоколов) исследований (испытаний) и измерений; дата прекращения действия декларации (при наступлении оснований)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Факт внесения сведений о результатах СОУТ в ФГИС СОУТ; копии подтверждающих документов; сведения по ч. 2 ст. 18, переданные в информационную систему учета</t>
+          <t>Работодатель (руководитель юридического лица / индивидуальный предприниматель)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Организация, проводящая СОУТ</t>
+          <t>Подача (передача) декларации в территориальный орган Роструда лично, почтой либо в форме электронного документа с УКЭП через официальный сайт Роструда; подписание декларации</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Уведомление работодателя в течение 3 рабочих дней со дня внесения сведений; направление переданных сведений</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Бумага (заказное почтовое отправление с уведомлением) либо электронный документ с УКЭП</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
+          <t>Бумага либо электронный документ, подписанный УКЭП работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -714,46 +692,41 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
+          <t>Приказ Минтруда России от 17.06.2021 № 406н; Федеральный закон от 28.12.2013 № 426-ФЗ</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ч. 3 ст. 18 Федерального закона № 426-ФЗ</t>
+          <t>п. 3, 4 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н); ч. 3 ст. 11 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Уведомление о внесении сведений в ФГИС СОУТ / переданные сведения</t>
+          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ФГИС СОУТ</t>
+          <t>Сведения о поступивших декларациях (состав сведений — п. 6 Порядка формирования и ведения реестра)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Сведения о внесении результатов СОУТ в ФГИС СОУТ (получение от организации, проводившей СОУТ)</t>
+          <t>Роструд / территориальный орган Роструда (ГИТ)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Работодатель</t>
+          <t>Внесение сведений о декларации в реестр в течение 15 рабочих дней со дня поступления декларации (на бумаге) или получения электронной формы, подписанной УКЭП</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Получение уведомления и сведений</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Бумага / электронный документ с УКЭП</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
+          <t>Запись реестра (электронный учет)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -764,46 +737,41 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ч. 4 ст. 18 Федерального закона № 426-ФЗ</t>
+          <t>ч. 5, 6 ст. 11 Федерального закона № 426-ФЗ; п. 3, 5 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Сведения в отношении объектов учета (при неисполнении организацией, проводившей СОУТ, обязанностей по передаче в ФГИС СОУТ)</t>
+          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ФГИС СОУТ (через территориальный орган Роструда)</t>
+          <t>Сведения о прекращении действия декларации (в том числе при выявлении недостоверности сведений, указанных в декларации, — внесение записи о прекращении действия декларации)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Имеющиеся у работодателя сведения в отношении объектов учета, указанных в ч. 2 ст. 18</t>
+          <t>Роструд / территориальный орган Роструда (ГИТ)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Работодатель</t>
+          <t>Внесение в реестр записи о прекращении действия декларации (при недостоверности сведений — в течение 5 рабочих дней с момента выявления)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Инициация / передача сведений в территориальный орган Роструда (ГИТ), в т.ч. в электронной форме (право работодателя)</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Электронный / иной документ с имеющимися сведениями</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>Запись реестра (электронный учет)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="100" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -814,397 +782,96 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 775н "Об утверждении Порядка проведения государственной экспертизы условий труда"</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ч. 5 ст. 18 Федерального закона № 426-ФЗ</t>
+          <t>п. 47 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Сведения в отношении объектов учета (результаты СОУТ)</t>
+          <t>ФГИС СОУТ</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>ФГИС СОУТ</t>
+          <t>Сведения о результатах проведенной государственной экспертизы качества специальной оценки условий труда</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Сведения в отношении объектов учета, указанных в ч. 2 ст. 18 (полученные от работодателя при неисполнении организацией, проводившей СОУТ, обязанностей по ч. 1 и 3 ст. 18)</t>
+          <t>Орган исполнительной власти субъекта Российской Федерации в области охраны труда (орган государственной экспертизы условий труда)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Территориальный орган Роструда (ГИТ)</t>
+          <t>Направление (передача) сведений о результатах экспертизы качества СОУТ во ФГИС СОУТ</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Передача сведений в ФГИС СОУТ; подписание УКЭП</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Электронный документ, подписанный УКЭП</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ (специальная оценка условий труда)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>ч. 1–3 ст. 11 Федерального закона № 426-ФЗ; п. 1–4 Порядка подачи декларации (прил. № 2 к приказу № 406н)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда (Роструд); подача — лично / почтой либо через официальный сайт Роструда (электронная форма); срок подачи — не позднее 30 рабочих дней со дня внесения сведений о результатах СОУТ в ФГИС СОУТ</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Сведения по форме декларации (прил. № 1 к приказу № 406н): данные работодателя; рабочие места, в отношении которых декларируется соответствие; основание (реквизиты заключения эксперта и/или протоколов исследований/измерений); сведения об организации, проводившей СОУТ; при аналогичных РМ — сведения обо всех аналогичных РМ</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель юридического лица / индивидуальный предприниматель)</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Инициация; подписание (руководитель ЮЛ — с печатью при наличии; ИП — лично; при электронной подаче — УКЭП); передача (подача) в территориальный орган Роструда (ГИТ)</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Бумага либо электронный документ, подписанный УКЭП работодателя</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ (специальная оценка условий труда)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 17.06.2021 № 406н</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>п. 1, 3, 4, 6 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н); ч. 3 ст. 11 Федерального закона № 426-ФЗ</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Запись в реестре деклараций / сведения о регистрации декларации</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда (формирование и ведение — Роструд и его территориальные органы)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>В реестр: полное наименование ЮЛ / ФИО ИП; место нахождения и деятельности; ИНН; ОГРН; полное наименование организации, проводившей СОУТ; перечень РМ (индивидуальный номер, численность работников); реквизиты заключения эксперта и/или протоколов; дата прекращения действия декларации (при наступлении оснований)</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Роструд / территориальный орган Роструда (ГИТ)</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Внесение сведений о декларации в реестр в течение 15 рабочих дней со дня поступления; техническое функционирование реестра; размещение открытых сведений на сайте Роструда; обмен информацией с иными информационными системами</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Запись реестра (электронный учет); при бумажной декларации — заполнение раздела «Сведения о регистрации декларации»</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ (специальная оценка условий труда)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>ч. 5–6 ст. 11 Федерального закона № 426-ФЗ; п. 3, 5 Порядка формирования и ведения реестра (прил. № 3 к приказу № 406н); также отражение во ФГИС СОУТ — пп. «и» п. 2 ч. 2 ст. 18 Федерального закона № 426-ФЗ</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Решение / запись о прекращении действия декларации</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Реестр деклараций (Роструд); ФГИС СОУТ (сведения о принятии решения о прекращении действия декларации — объект учета)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Сведения о прекращении действия декларации (в т.ч. при НС/профзаболеваниях по вине вредных факторов, нарушениях ОТ при госконтроле, недостоверности сведений в декларации)</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Роструд / территориальный орган Роструда (ГИТ)</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Принятие решения о прекращении действия декларации; внесение записи в реестр (при недостоверности — в течение 5 рабочих дней с момента выявления); обеспечение отражения во ФГИС СОУТ как объекта учета</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Решение / запись реестра; сведения во ФГИС СОУТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ (специальная оценка условий труда)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 29.10.2021 № 775н "Об утверждении Порядка проведения государственной экспертизы условий труда"</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>п. 14 Порядка проведения государственной экспертизы условий труда (прил. к приказу № 775н)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Заявление о проведении государственной экспертизы условий труда с прилагаемыми документами</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ) — один из способов подачи</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Заявление и документы по п. 11–13 Порядка (в т.ч. отчет о СОУТ с информацией о размещении во ФГИС СОУТ для отчетов после 01.01.2020)</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Заявитель (работодатель; работник; профсоюз / представительный орган; организация, проводившая СОУТ; страховщик; ГИТ; суд; Роспотребнадзор — по основаниям Порядка)</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Инициация; передача (подача) заявления и документов, в т.ч. через ЕПГУ / Интернет</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Бумага (лично / заказное почтовое отправление) либо электронный документ, в т.ч. через ЕПГУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ (специальная оценка условий труда)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 29.10.2021 № 775н</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>п. 47 Порядка проведения государственной экспертизы условий труда (прил. к приказу № 775н)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Заключение государственной экспертизы условий труда (экспертиза качества СОУТ) / сведения о результатах экспертизы качества СОУТ</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>ФГИС СОУТ</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Сведения о результатах проведенной государственной экспертизы качества специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Орган исполнительной власти субъекта РФ в области охраны труда (орган государственной экспертизы условий труда)</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Передача (направление) сведений о результатах экспертизы качества СОУТ во ФГИС СОУТ</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Сведения / электронная передача во ФГИС СОУТ (на основании заключения госэкспертизы)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ (специальная оценка условий труда)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 29.10.2021 № 775н</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>п. 12, 13, 15, 23, 26–31 Порядка (прил. к приказу № 775н)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Отчет о проведении СОУТ / материалы для государственной экспертизы; использование сведений ФГИС СОУТ</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>ФГИС СОУТ</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Использование при госэкспертизе сведений, содержащихся во ФГИС СОУТ (наличие/размещение отчета; сопоставление данных отчета с ФГИС СОУТ; межведомственные запросы; основания непроведения экспертизы при отсутствии отчета во ФГИС СОУТ и др.)</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Орган государственной экспертизы условий труда</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Получение / использование сведений из ФГИС СОУТ (не передача результатов СОУТ, а запрос и анализ данных ГИС)</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Сведения ФГИС СОУТ (использование при проведении экспертизы)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ (специальная оценка условий труда)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 08.09.2016 № 501н; Федеральный закон от 28.12.2013 № 426-ФЗ (ч. 4 ст. 24); связанно: Приказ Минтруда России от 03.11.2015 № 843н (п. 9 Порядка) — внесение оператором во ФГИС СОУТ</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Порядок, утв. приказом № 501н (рассмотрение разногласий / несогласия с результатами экспертизы качества СОУТ); ч. 4 ст. 24 Федерального закона № 426-ФЗ; п. 9 Порядка, утв. приказом № 843н (внесение во ФГИС СОУТ)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Заключение о рассмотрении разногласий (несогласия) с результатами экспертизы качества СОУТ</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>ФГИС СОУТ</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Результаты рассмотрения разногласий / несогласия: сведения о работодателе и организации, проводившей СОУТ; сведения о результатах госэкспертизы; реквизиты заключения о рассмотрении разногласий и содержащиеся в нем выводы (необходимость повторной экспертизы качества СОУТ на безвозмездной основе либо отсутствие правовых оснований для повторной экспертизы). Прямой нормы о передаче в ГИС в тексте приказа № 501н нет — внесение осуществляет оператор ФГИС СОУТ (Минтруд России) в течение 10 рабочих дней со дня утверждения заключения</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Заявитель (работник; профсоюз / объединение / представительный орган; работодатель / объединение; страховщик; ГИТ; организация, проводившая СОУТ) — инициация заявления; Минтруд России (оператор ФГИС СОУТ) — внесение сведений во ФГИС СОУТ</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Инициация заявления (заявитель); рассмотрение и утверждение заключения (Минтруд); внесение сведений во ФГИС СОУТ (оператор)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Заявление и заключение о рассмотрении разногласий (несогласия); сведения во ФГИС СОУТ</t>
+          <t>Сведения / электронная передача во ФГИС СОУТ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J15"/>
+  <autoFilter ref="A1:I8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Критерий включения</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>В таблицу включены только положения НПА, где прямо указана передача / внесение сведений в ГИС (информационную систему учета / реестр).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Исключено</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Уведомления работодателя об идентификационном номере и о внесении сведений в ФГИС СОУТ (ч. 6 ст. 8, ч. 3 ст. 18 426-ФЗ; п. 3 Методики 817н) — направляются работодателю вне ГИС. Использование ФГИС СОУТ при госэкспертизе как источника данных (приказ 775н) — не передача в ГИС. Приказ 501н не содержит прямой нормы о передаче сведений в ГИС. Приказ 817н сам по себе не устанавливает отдельную передачу уведомлений через ФГИС.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>По подаче через ЕПГУ (п. 14 приказа 775н)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Не включено: НПА допускает подачу заявления через ЕПГУ как способ направления документов в орган экспертизы, но не формулирует обязанность передачи определённого набора сведений в ЕПГУ как в ГИС учёта результатов СОУТ.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Примечания" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$I$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -816,8 +816,53 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ (специальная оценка условий труда)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 29.10.2021 № 775н "Об утверждении Порядка проведения государственной экспертизы условий труда"</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>п. 14 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Заявление о проведении государственной экспертизы условий труда и документы, указанные в п. 11, 12 и 13 Порядка (в том числе отчет о проведении СОУТ с информацией о размещении во ФГИС СОУТ для отчетов, утвержденных после 01.01.2020, и иные документы по целям экспертизы)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Заявитель (в зависимости от основания и цели экспертизы — работодатель, работник, представительный орган работников, организация, проводившая СОУТ, страховщик, ГИТ, судебный орган, Роспотребнадзор и др. — по Порядку)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Представление (направление) заявления и документов в орган государственной экспертизы условий труда в виде электронного документа посредством сети «Интернет», в том числе с использованием ЕПГУ</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Электронный документ (в том числе посредством ЕПГУ); также допускается бумага (лично / заказное почтовое отправление) — п. 14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:I9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -867,7 +912,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Не включено: НПА допускает подачу заявления через ЕПГУ как способ направления документов в орган экспертизы, но не формулирует обязанность передачи определённого набора сведений в ЕПГУ как в ГИС учёта результатов СОУТ.</t>
+          <t>Включено по п. 14 приказа № 775н: заявление и документы могут быть направлены в виде электронного документа с использованием ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ).</t>
         </is>
       </c>
     </row>

--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Примечания" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,18 +440,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="100" customHeight="1">
+    <row r="2" ht="110" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -527,7 +527,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Сведения в отношении работодателя: полное наименование; идентификационный номер налогоплательщика; код причины постановки на учет в налоговом органе (пп. «а», «в», «в.1» п. 1 ч. 2 ст. 18 Федерального закона № 426-ФЗ) — для присвоения идентификационного номера предстоящей СОУТ</t>
+          <t>полное наименование работодателя; ИНН; КПП</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="100" customHeight="1">
+    <row r="3" ht="110" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -572,7 +572,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Сведения о результатах проведения СОУТ (объекты учета по ч. 2 ст. 18), в том числе в отношении рабочих мест, условия труда на которых декларируются: 1) о работодателе — полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда; 2) о рабочем месте — индивидуальный номер РМ; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда и по каждому вредному/опасному фактору (наименование, единицы измерения, измеренные значения, нормативы, продолжительность воздействия, сведения о снижении класса/подкласса с учетом СИЗ); основание прав на досрочную страховую пенсию по старости (при наличии); сведения о НС на производстве и профзаболеваниях за последние 5 лет; сведения о качестве результатов СОУТ; сведения о решении о прекращении действия декларации; 3) об организации, проводившей СОУТ — полное наименование; регистрационный номер в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах; сведения о средствах измерений; сведения, предусмотренные ч. 1.1 ст. 19. За исключением сведений, составляющих государственную или иную охраняемую законом тайну, с учетом требований о персональных данных</t>
+          <t>В отношении работодателя: полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда. В отношении рабочего места: индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда, а также класс (подкласс) по каждому вредному и (или) опасному производственному фактору (наименование, единицы измерения, измеренные значения, соответствующие нормативы, продолжительность воздействия, сведения о снижении класса (подкласса) с учетом оценки эффективности СИЗ); основание для формирования прав на досрочное назначение страховой пенсии по старости (при наличии); сведения о произошедших за последние пять лет несчастных случаях на производстве и о профессиональных заболеваниях; сведения о качестве результатов проведения СОУТ; сведения о принятии решения о прекращении действия декларации соответствия условий труда государственным нормативным требованиям охраны труда. В отношении организации, проводившей СОУТ: полное наименование; регистрационный номер записи в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах (ФИО, должность, регистрационный номер в реестре экспертов); сведения о применявшихся средствах измерений; сведения, предусмотренные для внесения в информационную систему учета в отношении организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="100" customHeight="1">
+    <row r="4" ht="110" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -607,7 +607,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ч. 4, 5 ст. 18 Федерального закона № 426-ФЗ</t>
+          <t>ч. 4 ст. 18 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -617,26 +617,26 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Сведения в отношении объектов учета, указанных в ч. 2 ст. 18 Федерального закона № 426-ФЗ (в случае невыполнения организацией, проводящей СОУТ, обязанностей по ч. 1 и 3 ст. 18)</t>
+          <t>В отношении работодателя: полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда. В отношении рабочего места: индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда, а также класс (подкласс) по каждому вредному и (или) опасному производственному фактору (наименование, единицы измерения, измеренные значения, соответствующие нормативы, продолжительность воздействия, сведения о снижении класса (подкласса) с учетом оценки эффективности СИЗ); основание для формирования прав на досрочное назначение страховой пенсии по старости (при наличии); сведения о произошедших за последние пять лет несчастных случаях на производстве и о профессиональных заболеваниях; сведения о качестве результатов проведения СОУТ; сведения о принятии решения о прекращении действия декларации соответствия условий труда государственным нормативным требованиям охраны труда. В отношении организации, проводившей СОУТ: полное наименование; регистрационный номер записи в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах (ФИО, должность, регистрационный номер в реестре экспертов); сведения о применявшихся средствах измерений; сведения, предусмотренные для внесения в информационную систему учета в отношении организации, проводящей СОУТ (имеющиеся у работодателя сведения)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Территориальный орган Роструда (государственная инспекция труда)</t>
+          <t>Работодатель</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Передача сведений в информационную систему учета в форме электронного документа, подписанного УКЭП (на основании сведений, представленных работодателем в территориальный орган)</t>
+          <t>Передача имеющихся сведений в территориальный орган Роструда (ГИТ), в том числе в электронной форме (право работодателя при невыполнении организацией, проводящей СОУТ, обязанностей по передаче результатов СОУТ в информационную систему учета)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="100" customHeight="1">
+          <t>Электронный документ / имеющиеся у работодателя сведения</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -647,41 +647,41 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ч. 1–3 ст. 11 Федерального закона № 426-ФЗ; п. 2–4 Порядка подачи декларации (прил. № 2 к приказу № 406н); п. 1, 3, 4, 6 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
+          <t>ч. 5 ст. 18 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда (формирование и ведение — Роструд и его территориальные органы)</t>
+          <t>ФГИС СОУТ</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Сведения о декларации, подлежащие внесению в реестр (п. 6 Порядка формирования и ведения реестра): полное наименование ЮЛ (ФИО ИП); место нахождения и место осуществления деятельности; ИНН; ОГРН; полное наименование организации, проводившей СОУТ; перечень рабочих мест (индивидуальный номер РМ, численность работников); реквизиты заключения эксперта и (или) протокола (протоколов) исследований (испытаний) и измерений; дата прекращения действия декларации (при наступлении оснований)</t>
+          <t>В отношении работодателя: полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда. В отношении рабочего места: индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда, а также класс (подкласс) по каждому вредному и (или) опасному производственному фактору (наименование, единицы измерения, измеренные значения, соответствующие нормативы, продолжительность воздействия, сведения о снижении класса (подкласса) с учетом оценки эффективности СИЗ); основание для формирования прав на досрочное назначение страховой пенсии по старости (при наличии); сведения о произошедших за последние пять лет несчастных случаях на производстве и о профессиональных заболеваниях; сведения о качестве результатов проведения СОУТ; сведения о принятии решения о прекращении действия декларации соответствия условий труда государственным нормативным требованиям охраны труда. В отношении организации, проводившей СОУТ: полное наименование; регистрационный номер записи в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах (ФИО, должность, регистрационный номер в реестре экспертов); сведения о применявшихся средствах измерений; сведения, предусмотренные для внесения в информационную систему учета в отношении организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель юридического лица / индивидуальный предприниматель)</t>
+          <t>Территориальный орган Роструда (государственная инспекция труда)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Подача (передача) декларации в территориальный орган Роструда лично, почтой либо в форме электронного документа с УКЭП через официальный сайт Роструда; подписание декларации</t>
+          <t>Передача сведений в информационную систему учета в форме электронного документа, подписанного УКЭП (в случае, указанном в ч. 4 ст. 18)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Бумага либо электронный документ, подписанный УКЭП работодателя</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1">
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -692,41 +692,41 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 17.06.2021 № 406н; Федеральный закон от 28.12.2013 № 426-ФЗ</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>п. 3, 4 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н); ч. 3 ст. 11 Федерального закона № 426-ФЗ</t>
+          <t>ч. 1–3 ст. 11 Федерального закона № 426-ФЗ; п. 2–4 Порядка подачи декларации (прил. № 2 к приказу № 406н); п. 1, 3, 4, 6 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда (формирование и ведение — Роструд и его территориальные органы)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Сведения о поступивших декларациях (состав сведений — п. 6 Порядка формирования и ведения реестра)</t>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Роструд / территориальный орган Роструда (ГИТ)</t>
+          <t>Работодатель (руководитель юридического лица / индивидуальный предприниматель)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Внесение сведений о декларации в реестр в течение 15 рабочих дней со дня поступления декларации (на бумаге) или получения электронной формы, подписанной УКЭП</t>
+          <t>Подача (передача) декларации в территориальный орган Роструда лично, почтой либо в форме электронного документа с УКЭП через официальный сайт Роструда; подписание декларации</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Запись реестра (электронный учет)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
+          <t>Бумага либо электронный документ, подписанный УКЭП работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -737,12 +737,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Приказ Минтруда России от 17.06.2021 № 406н; Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ч. 5, 6 ст. 11 Федерального закона № 426-ФЗ; п. 3, 5 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
+          <t>п. 3, 4 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н); ч. 3 ст. 11 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Сведения о прекращении действия декларации (в том числе при выявлении недостоверности сведений, указанных в декларации, — внесение записи о прекращении действия декларации)</t>
+          <t>полное наименование юридического лица (фамилия, имя, отчество (при наличии) индивидуального предпринимателя); место нахождения и место осуществления деятельности; ИНН; ОГРН; полное наименование организации, проводившей СОУТ; перечень рабочих мест (индивидуальный номер рабочего места, численность работников, занятых на данном рабочем месте); реквизиты заключения эксперта организации, проводившей СОУТ, и (или) протокола (протоколов) проведения исследований (испытаний) и измерений вредных и (или) опасных производственных факторов; дата прекращения действия декларации (при наступлении оснований)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Внесение в реестр записи о прекращении действия декларации (при недостоверности сведений — в течение 5 рабочих дней с момента выявления)</t>
+          <t>Внесение сведений о декларации в реестр в течение 15 рабочих дней со дня поступления декларации (на бумаге) или получения электронной формы, подписанной УКЭП</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="100" customHeight="1">
+    <row r="8" ht="110" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -782,41 +782,41 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 29.10.2021 № 775н "Об утверждении Порядка проведения государственной экспертизы условий труда"</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>п. 47 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
+          <t>ч. 5, 6 ст. 11 Федерального закона № 426-ФЗ; п. 3, 5 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ФГИС СОУТ</t>
+          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Сведения о результатах проведенной государственной экспертизы качества специальной оценки условий труда</t>
+          <t>сведения о прекращении действия декларации соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Орган исполнительной власти субъекта Российской Федерации в области охраны труда (орган государственной экспертизы условий труда)</t>
+          <t>Роструд / территориальный орган Роструда (ГИТ)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Направление (передача) сведений о результатах экспертизы качества СОУТ во ФГИС СОУТ</t>
+          <t>Внесение в реестр записи о прекращении действия декларации (при недостоверности сведений — в течение 5 рабочих дней с момента выявления)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Сведения / электронная передача во ФГИС СОУТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1">
+          <t>Запись реестра (электронный учет)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -832,37 +832,82 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>п. 47 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>ФГИС СОУТ</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>сведения о результатах проведенной государственной экспертизы качества специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Орган исполнительной власти субъекта Российской Федерации в области охраны труда (орган государственной экспертизы условий труда)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Направление (передача) сведений о результатах экспертизы качества СОУТ во ФГИС СОУТ</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Сведения / электронная передача во ФГИС СОУТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ (специальная оценка условий труда)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 29.10.2021 № 775н "Об утверждении Порядка проведения государственной экспертизы условий труда"</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>п. 14 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Заявление о проведении государственной экспертизы условий труда и документы, указанные в п. 11, 12 и 13 Порядка (в том числе отчет о проведении СОУТ с информацией о размещении во ФГИС СОУТ для отчетов, утвержденных после 01.01.2020, и иные документы по целям экспертизы)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Заявитель (в зависимости от основания и цели экспертизы — работодатель, работник, представительный орган работников, организация, проводившая СОУТ, страховщик, ГИТ, судебный орган, Роспотребнадзор и др. — по Порядку)</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Заявление о проведении государственной экспертизы условий труда с прилагаемыми документами</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Заявитель (в зависимости от основания и цели экспертизы — работодатель, работник, представительный орган работников, организация, проводившая СОУТ, страховщик, ГИТ, судебный орган, Роспотребнадзор и др.)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Представление (направление) заявления и документов в орган государственной экспертизы условий труда в виде электронного документа посредством сети «Интернет», в том числе с использованием ЕПГУ</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Электронный документ (в том числе посредством ЕПГУ); также допускается бумага (лично / заказное почтовое отправление) — п. 14</t>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Электронный документ (в том числе посредством ЕПГУ); также допускается бумага (лично / заказное почтовое отправление)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I9"/>
+  <autoFilter ref="A1:I10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -873,14 +918,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="50" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Критерий включения</t>
@@ -888,31 +933,43 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>В таблицу включены только положения НПА, где прямо указана передача / внесение сведений в ГИС (информационную систему учета / реестр).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
+          <t>В таблицу включаются положения, где НПА прямо указывает передачу / внесение сведений в ГИС (информационную систему учета / реестр / ЕПГУ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>Участник передачи</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Указывается лицо (орган), которое по тексту НПА осуществляет передачу. По ч. 4 ст. 18 Федерального закона № 426-ФЗ сведения передает работодатель в территориальный орган Роструда; по ч. 5 ст. 18 — территориальный орган передает сведения во ФГИС СОУТ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Сведения, подлежащие передачи</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>В столбце указывается только перечень сведений без ссылок на статьи и пункты; если передается документ целиком — его наименование.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="50" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>Исключено</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Уведомления работодателя об идентификационном номере и о внесении сведений в ФГИС СОУТ (ч. 6 ст. 8, ч. 3 ст. 18 426-ФЗ; п. 3 Методики 817н) — направляются работодателю вне ГИС. Использование ФГИС СОУТ при госэкспертизе как источника данных (приказ 775н) — не передача в ГИС. Приказ 501н не содержит прямой нормы о передаче сведений в ГИС. Приказ 817н сам по себе не устанавливает отдельную передачу уведомлений через ФГИС.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>По подаче через ЕПГУ (п. 14 приказа 775н)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Включено по п. 14 приказа № 775н: заявление и документы могут быть направлены в виде электронного документа с использованием ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ).</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Уведомления работодателя вне ГИС (сообщение идентификационного номера, уведомление о внесении сведений во ФГИС). Использование ФГИС как источника при госэкспертизе. Приказ № 501н — без прямой нормы о передаче в ГИС.</t>
         </is>
       </c>
     </row>

--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Передача сведений в ГИС" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Примечания" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$I$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -64,15 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -448,9 +444,9 @@
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -501,7 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="110" customHeight="1">
+    <row r="2" ht="95" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -527,7 +523,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>полное наименование работодателя; ИНН; КПП</t>
+          <t>полное наименование работодателя; ИНН работодателя; КПП работодателя</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -546,7 +542,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="110" customHeight="1">
+    <row r="3" ht="95" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -572,7 +568,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>В отношении работодателя: полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда. В отношении рабочего места: индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда, а также класс (подкласс) по каждому вредному и (или) опасному производственному фактору (наименование, единицы измерения, измеренные значения, соответствующие нормативы, продолжительность воздействия, сведения о снижении класса (подкласса) с учетом оценки эффективности СИЗ); основание для формирования прав на досрочное назначение страховой пенсии по старости (при наличии); сведения о произошедших за последние пять лет несчастных случаях на производстве и о профессиональных заболеваниях; сведения о качестве результатов проведения СОУТ; сведения о принятии решения о прекращении действия декларации соответствия условий труда государственным нормативным требованиям охраны труда. В отношении организации, проводившей СОУТ: полное наименование; регистрационный номер записи в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах (ФИО, должность, регистрационный номер в реестре экспертов); сведения о применявшихся средствах измерений; сведения, предусмотренные для внесения в информационную систему учета в отношении организации, проводящей СОУТ</t>
+          <t>в отношении работодателя — полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда; в отношении рабочего места — индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда; по каждому вредному и (или) опасному производственному фактору — наименование, единицы измерения, измеренные значения, нормативы (гигиенические нормативы), продолжительность воздействия, сведения о снижении класса (подкласса) с учетом эффективности СИЗ; основание прав на досрочную страховую пенсию по старости (при наличии); сведения о несчастных случаях на производстве и профессиональных заболеваниях за последние пять лет; сведения о качестве результатов СОУТ; сведения о решении о прекращении действия декларации соответствия условий труда; в отношении организации, проводившей СОУТ — полное наименование; регистрационный номер в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах (ФИО, должность, регистрационный номер в реестре экспертов); сведения о средствах измерений (наименование, номер в Федеральном информационном фонде по обеспечению единства измерений, заводской номер, дата окончания поверки, дата измерений, наименования измерявшихся факторов); иные сведения об организации, проводившей СОУТ, предусмотренные законом</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -591,7 +587,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="110" customHeight="1">
+    <row r="4" ht="95" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -607,7 +603,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ч. 4 ст. 18 Федерального закона № 426-ФЗ</t>
+          <t>ч. 4, 5 ст. 18 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -617,26 +613,26 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>В отношении работодателя: полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда. В отношении рабочего места: индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда, а также класс (подкласс) по каждому вредному и (или) опасному производственному фактору (наименование, единицы измерения, измеренные значения, соответствующие нормативы, продолжительность воздействия, сведения о снижении класса (подкласса) с учетом оценки эффективности СИЗ); основание для формирования прав на досрочное назначение страховой пенсии по старости (при наличии); сведения о произошедших за последние пять лет несчастных случаях на производстве и о профессиональных заболеваниях; сведения о качестве результатов проведения СОУТ; сведения о принятии решения о прекращении действия декларации соответствия условий труда государственным нормативным требованиям охраны труда. В отношении организации, проводившей СОУТ: полное наименование; регистрационный номер записи в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах (ФИО, должность, регистрационный номер в реестре экспертов); сведения о применявшихся средствах измерений; сведения, предусмотренные для внесения в информационную систему учета в отношении организации, проводящей СОУТ (имеющиеся у работодателя сведения)</t>
+          <t>в отношении работодателя — полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда; в отношении рабочего места — индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда и сведения по вредным и (или) опасным производственным факторам; основание прав на досрочную страховую пенсию по старости (при наличии); сведения о несчастных случаях на производстве и профессиональных заболеваниях за последние пять лет; сведения о качестве результатов СОУТ; сведения о решении о прекращении действия декларации; в отношении организации, проводившей СОУТ — полное наименование; регистрационный номер в реестре; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории; сведения об экспертах; сведения о средствах измерений; иные сведения об организации, проводившей СОУТ, предусмотренные законом</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Работодатель</t>
+          <t>Территориальный орган Роструда (государственная инспекция труда)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Передача имеющихся сведений в территориальный орган Роструда (ГИТ), в том числе в электронной форме (право работодателя при невыполнении организацией, проводящей СОУТ, обязанностей по передаче результатов СОУТ в информационную систему учета)</t>
+          <t>Передача сведений в информационную систему учета в форме электронного документа, подписанного УКЭП (на основании сведений, представленных работодателем в территориальный орган)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Электронный документ / имеющиеся у работодателя сведения</t>
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="110" customHeight="1">
+    <row r="5" ht="95" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -647,41 +643,41 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ч. 5 ст. 18 Федерального закона № 426-ФЗ</t>
+          <t>ч. 1–3 ст. 11 Федерального закона № 426-ФЗ; п. 2–4 Порядка подачи декларации (прил. № 2 к приказу № 406н); п. 1, 3, 4, 6 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ФГИС СОУТ</t>
+          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда (формирование и ведение — Роструд и его территориальные органы)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>В отношении работодателя: полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда. В отношении рабочего места: индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда, а также класс (подкласс) по каждому вредному и (или) опасному производственному фактору (наименование, единицы измерения, измеренные значения, соответствующие нормативы, продолжительность воздействия, сведения о снижении класса (подкласса) с учетом оценки эффективности СИЗ); основание для формирования прав на досрочное назначение страховой пенсии по старости (при наличии); сведения о произошедших за последние пять лет несчастных случаях на производстве и о профессиональных заболеваниях; сведения о качестве результатов проведения СОУТ; сведения о принятии решения о прекращении действия декларации соответствия условий труда государственным нормативным требованиям охраны труда. В отношении организации, проводившей СОУТ: полное наименование; регистрационный номер записи в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах (ФИО, должность, регистрационный номер в реестре экспертов); сведения о применявшихся средствах измерений; сведения, предусмотренные для внесения в информационную систему учета в отношении организации, проводящей СОУТ</t>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Территориальный орган Роструда (государственная инспекция труда)</t>
+          <t>Работодатель (руководитель юридического лица / индивидуальный предприниматель)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Передача сведений в информационную систему учета в форме электронного документа, подписанного УКЭП (в случае, указанном в ч. 4 ст. 18)</t>
+          <t>Подача (передача) декларации в территориальный орган Роструда лично, почтой либо в форме электронного документа с УКЭП через официальный сайт Роструда; подписание декларации</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
+          <t>Бумага либо электронный документ, подписанный УКЭП работодателя</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="110" customHeight="1">
+    <row r="6" ht="95" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -692,41 +688,41 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Приказ Минтруда России от 17.06.2021 № 406н; Федеральный закон от 28.12.2013 № 426-ФЗ</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ч. 1–3 ст. 11 Федерального закона № 426-ФЗ; п. 2–4 Порядка подачи декларации (прил. № 2 к приказу № 406н); п. 1, 3, 4, 6 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
+          <t>п. 3, 4 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н); ч. 3 ст. 11 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда (формирование и ведение — Роструд и его территориальные органы)</t>
+          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>полное наименование юридического лица (ФИО индивидуального предпринимателя); место нахождения и место осуществления деятельности; ИНН; ОГРН; полное наименование организации, проводившей СОУТ; перечень рабочих мест (индивидуальный номер рабочего места, численность работников); реквизиты заключения эксперта и (или) протокола (протоколов) исследований (испытаний) и измерений вредных и (или) опасных производственных факторов; дата прекращения действия декларации (при наступлении оснований)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель юридического лица / индивидуальный предприниматель)</t>
+          <t>Роструд / территориальный орган Роструда (ГИТ)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Подача (передача) декларации в территориальный орган Роструда лично, почтой либо в форме электронного документа с УКЭП через официальный сайт Роструда; подписание декларации</t>
+          <t>Внесение сведений о декларации в реестр в течение 15 рабочих дней со дня поступления декларации (на бумаге) или получения электронной формы, подписанной УКЭП</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Бумага либо электронный документ, подписанный УКЭП работодателя</t>
+          <t>Запись реестра (электронный учет)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="110" customHeight="1">
+    <row r="7" ht="95" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -737,12 +733,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 17.06.2021 № 406н; Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>п. 3, 4 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н); ч. 3 ст. 11 Федерального закона № 426-ФЗ</t>
+          <t>ч. 5, 6 ст. 11 Федерального закона № 426-ФЗ; п. 3, 5 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>полное наименование юридического лица (фамилия, имя, отчество (при наличии) индивидуального предпринимателя); место нахождения и место осуществления деятельности; ИНН; ОГРН; полное наименование организации, проводившей СОУТ; перечень рабочих мест (индивидуальный номер рабочего места, численность работников, занятых на данном рабочем месте); реквизиты заключения эксперта организации, проводившей СОУТ, и (или) протокола (протоколов) проведения исследований (испытаний) и измерений вредных и (или) опасных производственных факторов; дата прекращения действия декларации (при наступлении оснований)</t>
+          <t>дата прекращения действия декларации / запись о прекращении действия декларации</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -762,7 +758,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Внесение сведений о декларации в реестр в течение 15 рабочих дней со дня поступления декларации (на бумаге) или получения электронной формы, подписанной УКЭП</t>
+          <t>Внесение в реестр записи о прекращении действия декларации (при недостоверности сведений — в течение 5 рабочих дней с момента выявления)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -771,7 +767,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="110" customHeight="1">
+    <row r="8" ht="95" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -782,41 +778,41 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 775н "Об утверждении Порядка проведения государственной экспертизы условий труда"</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ч. 5, 6 ст. 11 Федерального закона № 426-ФЗ; п. 3, 5 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
+          <t>п. 47 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>ФГИС СОУТ</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>сведения о прекращении действия декларации соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>сведения о результатах проведенной государственной экспертизы качества специальной оценки условий труда</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Роструд / территориальный орган Роструда (ГИТ)</t>
+          <t>Орган исполнительной власти субъекта Российской Федерации в области охраны труда (орган государственной экспертизы условий труда)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Внесение в реестр записи о прекращении действия декларации (при недостоверности сведений — в течение 5 рабочих дней с момента выявления)</t>
+          <t>Направление (передача) сведений о результатах экспертизы качества СОУТ во ФГИС СОУТ</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Запись реестра (электронный учет)</t>
+          <t>Сведения / электронная передача во ФГИС СОУТ</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="110" customHeight="1">
+    <row r="9" ht="95" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -832,148 +828,37 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>п. 47 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
+          <t>п. 14 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ФГИС СОУТ</t>
+          <t>ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>сведения о результатах проведенной государственной экспертизы качества специальной оценки условий труда</t>
+          <t>Заявление о проведении государственной экспертизы условий труда; документы, прилагаемые к заявлению (в том числе отчет о проведении специальной оценки условий труда и иные документы по целям экспертизы)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Орган исполнительной власти субъекта Российской Федерации в области охраны труда (орган государственной экспертизы условий труда)</t>
+          <t>Заявитель (в зависимости от основания и цели экспертизы — работодатель, работник, представительный орган работников, организация, проводившая СОУТ, страховщик, ГИТ, судебный орган, Роспотребнадзор и др. — по Порядку)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Направление (передача) сведений о результатах экспертизы качества СОУТ во ФГИС СОУТ</t>
+          <t>Представление (направление) заявления и документов в орган государственной экспертизы условий труда в виде электронного документа посредством сети «Интернет», в том числе с использованием ЕПГУ</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Сведения / электронная передача во ФГИС СОУТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ (специальная оценка условий труда)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 29.10.2021 № 775н "Об утверждении Порядка проведения государственной экспертизы условий труда"</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>п. 14 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Заявление о проведении государственной экспертизы условий труда с прилагаемыми документами</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Заявитель (в зависимости от основания и цели экспертизы — работодатель, работник, представительный орган работников, организация, проводившая СОУТ, страховщик, ГИТ, судебный орган, Роспотребнадзор и др.)</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Представление (направление) заявления и документов в орган государственной экспертизы условий труда в виде электронного документа посредством сети «Интернет», в том числе с использованием ЕПГУ</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Электронный документ (в том числе посредством ЕПГУ); также допускается бумага (лично / заказное почтовое отправление)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I10"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="50" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Критерий включения</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>В таблицу включаются положения, где НПА прямо указывает передачу / внесение сведений в ГИС (информационную систему учета / реестр / ЕПГУ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="50" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Участник передачи</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Указывается лицо (орган), которое по тексту НПА осуществляет передачу. По ч. 4 ст. 18 Федерального закона № 426-ФЗ сведения передает работодатель в территориальный орган Роструда; по ч. 5 ст. 18 — территориальный орган передает сведения во ФГИС СОУТ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="50" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Сведения, подлежащие передачи</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>В столбце указывается только перечень сведений без ссылок на статьи и пункты; если передается документ целиком — его наименование.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="50" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Исключено</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Уведомления работодателя вне ГИС (сообщение идентификационного номера, уведомление о внесении сведений во ФГИС). Использование ФГИС как источника при госэкспертизе. Приказ № 501н — без прямой нормы о передаче в ГИС.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:I9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Передача сведений в ГИС" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Передача сведений в ГИС'!$A$1:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -857,8 +857,53 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="110" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ (специальная оценка условий труда)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 08.09.2016 № 501н "Об утверждении Порядка рассмотрения разногласий по вопросам проведения экспертизы качества специальной оценки условий труда, несогласия работников, профессиональных союзов, их объединений, иных уполномоченных работниками представительных органов, работодателей, их объединений, страховщиков, территориальных органов федерального органа исполнительной власти, уполномоченного на проведение федерального государственного надзора за соблюдением трудового законодательства и иных нормативных правовых актов, содержащих нормы трудового права, организаций, проводивших специальную оценку условий труда, с результатами экспертизы качества специальной оценки условий труда"</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>п. 2, 3, 5 Порядка (приложение к приказу № 501н)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Заявление о рассмотрении разногласий (несогласия) с результатами экспертизы качества специальной оценки условий труда; копия заключения государственной экспертизы условий труда</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Заявитель (работник; профессиональный союз / объединение / иной уполномоченный работниками представительный орган; работодатель / объединение работодателей; страховщик; территориальный орган Роструда (ГИТ); организация, проводившая СОУТ)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Представление (направление) заявления и прилагаемых документов в Минтруд России в виде электронного документа посредством сети «Интернет», в том числе с использованием ЕПГУ; подписание электронной подписью</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Электронный документ (в том числе посредством ЕПГУ); также допускается бумага (лично / заказное почтовое отправление)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I9"/>
+  <autoFilter ref="A1:I10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -63,12 +63,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -436,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -451,47 +457,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Процедура СУОТ</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Основополагающий НПА</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Где прописано (статья, пункт)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>ГИС</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Сведения, подлежащие передачи</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Участник передачи</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Роль участника</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Вид документа</t>
         </is>
@@ -899,6 +905,366 @@
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Электронный документ (в том числе посредством ЕПГУ); также допускается бумага (лично / заказное почтовое отправление)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Обязательные предварительные и периодические медицинские осмотры</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Приказ Министерства здравоохранения РФ от 28.01.2021 № 29н "Об утверждении Порядка проведения обязательных предварительных и периодических медицинских осмотров работников, предусмотренных частью четвертой статьи 213 Трудового кодекса Российской Федерации, перечня медицинских противопоказаний к осуществлению работ с вредными и (или) опасными производственными факторами, а также работам, при выполнении которых проводятся обязательные предварительные и периодические медицинские осмотры"</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>п. 17 Порядка проведения обязательных предварительных и периодических медицинских осмотров (приложение № 1 к приказу № 29н)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Единая государственная информационная система в сфере здравоохранения (ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Заключение по результатам предварительного медицинского осмотра</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация, проводившая предварительный медицинский осмотр</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Внесение заключения в форме электронного документа в ЕГИСЗ не позднее 5 рабочих дней (при наличии у медицинской организации доступа к ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ (внесение в ЕГИСЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Обязательные предварительные и периодические медицинские осмотры</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Приказ Министерства здравоохранения РФ от 28.01.2021 № 29н "Об утверждении Порядка проведения обязательных предварительных и периодических медицинских осмотров работников, предусмотренных частью четвертой статьи 213 Трудового кодекса Российской Федерации, перечня медицинских противопоказаний к осуществлению работ с вредными и (или) опасными производственными факторами, а также работам, при выполнении которых проводятся обязательные предварительные и периодические медицинские осмотры"</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>п. 34 Порядка проведения обязательных предварительных и периодических медицинских осмотров (приложение № 1 к приказу № 29н)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Единая государственная информационная система в сфере здравоохранения (ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Заключение по результатам периодического медицинского осмотра</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация, проводившая периодический медицинский осмотр</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Внесение заключения в форме электронного документа в ЕГИСЗ не позднее 5 рабочих дней (при наличии у медицинской организации доступа к ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ (внесение в ЕГИСЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Обязательные предварительные и периодические медицинские осмотры</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Приказ Министерства здравоохранения РФ от 28.01.2021 № 29н "Об утверждении Порядка проведения обязательных предварительных и периодических медицинских осмотров работников, предусмотренных частью четвертой статьи 213 Трудового кодекса Российской Федерации, перечня медицинских противопоказаний к осуществлению работ с вредными и (или) опасными производственными факторами, а также работам, при выполнении которых проводятся обязательные предварительные и периодические медицинские осмотры"</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>п. 7.1 Порядка проведения обязательных предварительных и периодических медицинских осмотров (приложение № 1 к приказу № 29н)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Федеральный реестр документов, содержащий сведения о результатах медицинского освидетельствования (ведется в ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Сообщение о наличии оснований для внеочередного медицинского освидетельствования и об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к владению оружием</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация (при выявлении у владельца оружия заболеваний, при которых противопоказано владение оружием)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере оборота оружия; подписание УКЭП медицинским работником и медицинской организацией</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Обязательное психиатрическое освидетельствование работников</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Приказ Министерства здравоохранения РФ от 20.05.2022 № 342н "Об утверждении порядка прохождения обязательного психиатрического освидетельствования работниками, осуществляющими отдельные виды деятельности, его периодичности, а также видов деятельности, при осуществлении которых проводится психиатрическое освидетельствование"</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>п. 14 Порядка прохождения обязательного психиатрического освидетельствования (приложение № 1 к приказу № 342н)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Федеральный реестр документов, содержащий сведения о результатах медицинского освидетельствования (ведется в ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Сообщение о наличии оснований для внеочередного медицинского освидетельствования и об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к владению оружием</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация (при выявлении у владельца оружия заболеваний, при которых противопоказано владение оружием)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере оборота оружия; подписание УКЭП медицинским работником и медицинской организацией</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Обязательное психиатрическое освидетельствование работников</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Приказ Министерства здравоохранения РФ от 20.05.2022 № 342н "Об утверждении порядка прохождения обязательного психиатрического освидетельствования работниками, осуществляющими отдельные виды деятельности, его периодичности, а также видов деятельности, при осуществлении которых проводится психиатрическое освидетельствование"</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>п. 15 Порядка прохождения обязательного психиатрического освидетельствования (приложение № 1 к приказу № 342н)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Федеральный реестр документов, содержащий сведения о результатах медицинского освидетельствования (ведется в ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Сообщение об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к исполнению обязанностей частного охранника</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация (при выявлении у частного охранника заболеваний, при которых противопоказано исполнять обязанности частного охранника)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере частной охранной деятельности; подписание УКЭП медицинским работником и медицинской организацией</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Обязательное психиатрическое освидетельствование работников</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Приказ Министерства здравоохранения РФ от 20.05.2022 № 342н "Об утверждении порядка прохождения обязательного психиатрического освидетельствования работниками, осуществляющими отдельные виды деятельности, его периодичности, а также видов деятельности, при осуществлении которых проводится психиатрическое освидетельствование"</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>п. 16 Порядка прохождения обязательного психиатрического освидетельствования (приложение № 1 к приказу № 342н)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Федеральный реестр документов, содержащий сведения о результатах медицинского освидетельствования (ведется в ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Сообщение об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к осуществлению частной детективной деятельности</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация (при выявлении у частного детектива заболеваний, при которых противопоказано осуществлять частную детективную деятельность)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере частной детективной деятельности; подписание УКЭП медицинским работником и медицинской организацией</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Медицинские осмотры с использованием медицинских изделий (дистанционная передача сведений о состоянии здоровья)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 30.05.2023 № 866 "Об особенностях проведения медицинских осмотров с использованием медицинских изделий, обеспечивающих автоматизированную дистанционную передачу информации о состоянии здоровья работников и дистанционный контроль состояния их здоровья"</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>п. 8 Особенностей проведения медицинских осмотров (приложение к постановлению № 866); п. 3 ч. 3 ст. 91.1 Федерального закона от 21.11.2011 № 323-ФЗ</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Единая государственная информационная система в сфере здравоохранения (ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>сведения о медицинских работниках, проводящих медицинские осмотры с использованием медицинских изделий</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация / иная организация, имеющая лицензию на медицинскую деятельность (в части медицинских работников, проводящих осмотры с использованием медицинских изделий)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Внесение сведений о медицинских работниках в ЕГИСЗ</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Сведения / запись в ЕГИСЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Медицинские осмотры с использованием медицинских изделий (дистанционная передача сведений о состоянии здоровья)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 30.05.2023 № 866 "Об особенностях проведения медицинских осмотров с использованием медицинских изделий, обеспечивающих автоматизированную дистанционную передачу информации о состоянии здоровья работников и дистанционный контроль состояния их здоровья"</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>п. 13 подп. "г" Особенностей проведения медицинских осмотров (приложение к постановлению № 866)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Орган или организация, уполномоченные Министерством транспорта Российской Федерации</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>сведения об оформленных в отношении водителей транспортных средств медицинских заключениях; сведения об условиях применения медицинских изделий</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация (или иная организация, осуществляющая медицинскую деятельность), проводившая медицинский осмотр с использованием медицинских изделий</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Передача сведений в орган (организацию), уполномоченный(ую) Минтрансом России, в соответствии с соглашением об информационном взаимодействии (в целях обеспечения достоверности результатов контроля целостности, актуальности сведений о поверке и условий применения медицинских изделий)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Сведения / электронная передача (по соглашению об информационном взаимодействии)</t>
         </is>
       </c>
     </row>

--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -1029,12 +1029,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Медицинская организация (при выявлении у владельца оружия заболеваний, при которых противопоказано владение оружием)</t>
+          <t>Медицинская организация, проводившая обязательный предварительный или периодический медицинский осмотр (при выявлении у владельца оружия заболеваний, при которых противопоказано владение оружием)</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере оборота оружия; подписание УКЭП медицинским работником и медицинской организацией</t>
+          <t>При выявлении противопоказаний к владению оружием в ходе обязательного предварительного или периодического медицинского осмотра по приказу № 29н: размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере оборота оружия; подписание УКЭП медицинским работником и медицинской организацией (содержание передачи совпадает с п. 14 приказа № 342н; отличие — процедура выявления: медосмотр, а не психиатрическое освидетельствование)</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Медицинская организация (при выявлении у владельца оружия заболеваний, при которых противопоказано владение оружием)</t>
+          <t>Медицинская организация, проводившая обязательное психиатрическое освидетельствование (при выявлении у владельца оружия заболеваний, при которых противопоказано владение оружием)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере оборота оружия; подписание УКЭП медицинским работником и медицинской организацией</t>
+          <t>При выявлении противопоказаний к владению оружием в ходе обязательного психиатрического освидетельствования по приказу № 342н: размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере оборота оружия; подписание УКЭП медицинским работником и медицинской организацией (содержание передачи совпадает с п. 7.1 приказа № 29н; отличие — процедура выявления: психиатрическое освидетельствование, а не медосмотр)</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">

--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Сообщение о наличии оснований для внеочередного медицинского освидетельствования и об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к владению оружием</t>
+          <t>Сообщение о наличии оснований для внеочередного медицинского освидетельствования и об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к владению оружием (выявлено в ходе обязательного предварительного или периодического медицинского осмотра по приказу № 29н)</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Сообщение о наличии оснований для внеочередного медицинского освидетельствования и об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к владению оружием</t>
+          <t>Сообщение о наличии оснований для внеочередного медицинского освидетельствования и об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к владению оружием (выявлено в ходе обязательного психиатрического освидетельствования по приказу № 342н)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">

--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -504,405 +504,405 @@
       </c>
     </row>
     <row r="2" ht="95" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>СОУТ (специальная оценка условий труда)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>ч. 6 ст. 8 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>ФГИС учета результатов проведения специальной оценки условий труда (ФГИС СОУТ)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>полное наименование работодателя; ИНН работодателя; КПП работодателя</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Передача сведений в информационную систему учета (до начала работ по СОУТ, но не позднее 5 рабочих дней со дня заключения договора)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Электронный документ (передача в ФГИС СОУТ)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="95" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>СОУТ (специальная оценка условий труда)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>ч. 1, 2, 3 ст. 18 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>ФГИС СОУТ</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>в отношении работодателя — полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда; в отношении рабочего места — индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда; по каждому вредному и (или) опасному производственному фактору — наименование, единицы измерения, измеренные значения, нормативы (гигиенические нормативы), продолжительность воздействия, сведения о снижении класса (подкласса) с учетом эффективности СИЗ; основание прав на досрочную страховую пенсию по старости (при наличии); сведения о несчастных случаях на производстве и профессиональных заболеваниях за последние пять лет; сведения о качестве результатов СОУТ; сведения о решении о прекращении действия декларации соответствия условий труда; в отношении организации, проводившей СОУТ — полное наименование; регистрационный номер в реестре организаций, проводящих СОУТ; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории (центра); сведения об экспертах (ФИО, должность, регистрационный номер в реестре экспертов); сведения о средствах измерений (наименование, номер в Федеральном информационном фонде по обеспечению единства измерений, заводской номер, дата окончания поверки, дата измерений, наименования измерявшихся факторов); иные сведения об организации, проводившей СОУТ, предусмотренные законом</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Передача сведений в информационную систему учета в течение 10 рабочих дней со дня утверждения отчета о проведении СОУТ; подписание УКЭП</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
         </is>
       </c>
     </row>
     <row r="4" ht="95" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>СОУТ (специальная оценка условий труда)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>ч. 4, 5 ст. 18 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>ФГИС СОУТ</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>в отношении работодателя — полное наименование; место нахождения и место осуществления деятельности; ИНН; КПП; ОГРН; код ОКВЭД; количество рабочих мест; количество рабочих мест, на которых проведена СОУТ; распределение рабочих мест по классам (подклассам) условий труда; в отношении рабочего места — индивидуальный номер рабочего места; код профессии; СНИЛС работника (работников); численность работников; класс (подкласс) условий труда и сведения по вредным и (или) опасным производственным факторам; основание прав на досрочную страховую пенсию по старости (при наличии); сведения о несчастных случаях на производстве и профессиональных заболеваниях за последние пять лет; сведения о качестве результатов СОУТ; сведения о решении о прекращении действия декларации; в отношении организации, проводившей СОУТ — полное наименование; регистрационный номер в реестре; ИНН; ОГРН; сведения об аккредитации испытательной лаборатории; сведения об экспертах; сведения о средствах измерений; иные сведения об организации, проводившей СОУТ, предусмотренные законом</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Территориальный орган Роструда (государственная инспекция труда)</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Передача сведений в информационную систему учета в форме электронного документа, подписанного УКЭП (на основании сведений, представленных работодателем в территориальный орган)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
         </is>
       </c>
     </row>
     <row r="5" ht="95" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>СОУТ (специальная оценка условий труда)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>ч. 1–3 ст. 11 Федерального закона № 426-ФЗ; п. 2–4 Порядка подачи декларации (прил. № 2 к приказу № 406н); п. 1, 3, 4, 6 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда (формирование и ведение — Роструд и его территориальные органы)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Работодатель (руководитель юридического лица / индивидуальный предприниматель)</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Подача (передача) декларации в территориальный орган Роструда лично, почтой либо в форме электронного документа с УКЭП через официальный сайт Роструда; подписание декларации</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Бумага либо электронный документ, подписанный УКЭП работодателя</t>
         </is>
       </c>
     </row>
     <row r="6" ht="95" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>СОУТ (специальная оценка условий труда)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 17.06.2021 № 406н; Федеральный закон от 28.12.2013 № 426-ФЗ</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>п. 3, 4 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н); ч. 3 ст. 11 Федерального закона № 426-ФЗ</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>полное наименование юридического лица (ФИО индивидуального предпринимателя); место нахождения и место осуществления деятельности; ИНН; ОГРН; полное наименование организации, проводившей СОУТ; перечень рабочих мест (индивидуальный номер рабочего места, численность работников); реквизиты заключения эксперта и (или) протокола (протоколов) исследований (испытаний) и измерений вредных и (или) опасных производственных факторов; дата прекращения действия декларации (при наступлении оснований)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Роструд / территориальный орган Роструда (ГИТ)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Внесение сведений о декларации в реестр в течение 15 рабочих дней со дня поступления декларации (на бумаге) или получения электронной формы, подписанной УКЭП</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Запись реестра (электронный учет)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="95" customHeight="1">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>СОУТ (специальная оценка условий труда)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ "О специальной оценке условий труда"; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>ч. 5, 6 ст. 11 Федерального закона № 426-ФЗ; п. 3, 5 Порядка формирования и ведения реестра деклараций (прил. № 3 к приказу № 406н)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>дата прекращения действия декларации / запись о прекращении действия декларации</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Роструд / территориальный орган Роструда (ГИТ)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Внесение в реестр записи о прекращении действия декларации (при недостоверности сведений — в течение 5 рабочих дней с момента выявления)</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Запись реестра (электронный учет)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="95" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>СОУТ (специальная оценка условий труда)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 775н "Об утверждении Порядка проведения государственной экспертизы условий труда"</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>п. 47 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>ФГИС СОУТ</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>сведения о результатах проведенной государственной экспертизы качества специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Орган исполнительной власти субъекта Российской Федерации в области охраны труда (орган государственной экспертизы условий труда)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Направление (передача) сведений о результатах экспертизы качества СОУТ во ФГИС СОУТ</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Сведения / электронная передача во ФГИС СОУТ</t>
         </is>
       </c>
     </row>
     <row r="9" ht="95" customHeight="1">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>СОУТ (специальная оценка условий труда)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 775н "Об утверждении Порядка проведения государственной экспертизы условий труда"</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>п. 14 Порядка проведения государственной экспертизы условий труда (приложение к приказу № 775н)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Заявление о проведении государственной экспертизы условий труда; документы, прилагаемые к заявлению (в том числе отчет о проведении специальной оценки условий труда и иные документы по целям экспертизы)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Заявитель (в зависимости от основания и цели экспертизы — работодатель, работник, представительный орган работников, организация, проводившая СОУТ, страховщик, ГИТ, судебный орган, Роспотребнадзор и др. — по Порядку)</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Представление (направление) заявления и документов в орган государственной экспертизы условий труда в виде электронного документа посредством сети «Интернет», в том числе с использованием ЕПГУ</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Электронный документ (в том числе посредством ЕПГУ); также допускается бумага (лично / заказное почтовое отправление)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>СОУТ (специальная оценка условий труда)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 08.09.2016 № 501н "Об утверждении Порядка рассмотрения разногласий по вопросам проведения экспертизы качества специальной оценки условий труда, несогласия работников, профессиональных союзов, их объединений, иных уполномоченных работниками представительных органов, работодателей, их объединений, страховщиков, территориальных органов федерального органа исполнительной власти, уполномоченного на проведение федерального государственного надзора за соблюдением трудового законодательства и иных нормативных правовых актов, содержащих нормы трудового права, организаций, проводивших специальную оценку условий труда, с результатами экспертизы качества специальной оценки условий труда"</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>п. 2, 3, 5 Порядка (приложение к приказу № 501н)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>ФГИС «Единый портал государственных и муниципальных услуг (функций)» (ЕПГУ)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Заявление о рассмотрении разногласий (несогласия) с результатами экспертизы качества специальной оценки условий труда; копия заключения государственной экспертизы условий труда</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Заявитель (работник; профессиональный союз / объединение / иной уполномоченный работниками представительный орган; работодатель / объединение работодателей; страховщик; территориальный орган Роструда (ГИТ); организация, проводившая СОУТ)</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Представление (направление) заявления и прилагаемых документов в Минтруд России в виде электронного документа посредством сети «Интернет», в том числе с использованием ЕПГУ; подписание электронной подписью</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Электронный документ (в том числе посредством ЕПГУ); также допускается бумага (лично / заказное почтовое отправление)</t>
         </is>
@@ -1049,17 +1049,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Обязательное психиатрическое освидетельствование работников</t>
+          <t>Обязательные предварительные и периодические медицинские осмотры</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Приказ Министерства здравоохранения РФ от 20.05.2022 № 342н "Об утверждении порядка прохождения обязательного психиатрического освидетельствования работниками, осуществляющими отдельные виды деятельности, его периодичности, а также видов деятельности, при осуществлении которых проводится психиатрическое освидетельствование"</t>
+          <t>Приказ Министерства здравоохранения РФ от 28.01.2021 № 29н "Об утверждении Порядка проведения обязательных предварительных и периодических медицинских осмотров работников, предусмотренных частью четвертой статьи 213 Трудового кодекса Российской Федерации, перечня медицинских противопоказаний к осуществлению работ с вредными и (или) опасными производственными факторами, а также работам, при выполнении которых проводятся обязательные предварительные и периодические медицинские осмотры"</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>п. 14 Порядка прохождения обязательного психиатрического освидетельствования (приложение № 1 к приказу № 342н)</t>
+          <t>п. 7(2) Порядка проведения обязательных предварительных и периодических медицинских осмотров (приложение № 1 к приказу № 29н; введен приказом Минздрава России от 29.04.2026 № 327н)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Сообщение о наличии оснований для внеочередного медицинского освидетельствования и об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к владению оружием (выявлено в ходе обязательного психиатрического освидетельствования по приказу № 342н)</t>
+          <t>Сообщение об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к исполнению обязанностей частного охранника (выявлено в ходе обязательного предварительного или периодического медицинского осмотра по приказу № 29н)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Медицинская организация, проводившая обязательное психиатрическое освидетельствование (при выявлении у владельца оружия заболеваний, при которых противопоказано владение оружием)</t>
+          <t>Медицинская организация, проводившая обязательный предварительный или периодический медицинский осмотр (при выявлении у частного охранника заболеваний, при которых противопоказано исполнять обязанности частного охранника)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>При выявлении противопоказаний к владению оружием в ходе обязательного психиатрического освидетельствования по приказу № 342н: размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере оборота оружия; подписание УКЭП медицинским работником и медицинской организацией (содержание передачи совпадает с п. 7.1 приказа № 29н; отличие — процедура выявления: психиатрическое освидетельствование, а не медосмотр)</t>
+          <t>При выявлении противопоказаний к исполнению обязанностей частного охранника в ходе обязательного предварительного или периодического медицинского осмотра по приказу № 29н: размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере частной охранной деятельности; подписание УКЭП медицинским работником и медицинской организацией (содержание передачи совпадает с п. 15 приказа № 342н; отличие — процедура выявления: медосмотр, а не психиатрическое освидетельствование)</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Обязательное психиатрическое освидетельствование работников</t>
+          <t>Обязательные предварительные и периодические медицинские осмотры</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Приказ Министерства здравоохранения РФ от 20.05.2022 № 342н "Об утверждении порядка прохождения обязательного психиатрического освидетельствования работниками, осуществляющими отдельные виды деятельности, его периодичности, а также видов деятельности, при осуществлении которых проводится психиатрическое освидетельствование"</t>
+          <t>Приказ Министерства здравоохранения РФ от 28.01.2021 № 29н "Об утверждении Порядка проведения обязательных предварительных и периодических медицинских осмотров работников, предусмотренных частью четвертой статьи 213 Трудового кодекса Российской Федерации, перечня медицинских противопоказаний к осуществлению работ с вредными и (или) опасными производственными факторами, а также работам, при выполнении которых проводятся обязательные предварительные и периодические медицинские осмотры"</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>п. 15 Порядка прохождения обязательного психиатрического освидетельствования (приложение № 1 к приказу № 342н)</t>
+          <t>п. 7(3) Порядка проведения обязательных предварительных и периодических медицинских осмотров (приложение № 1 к приказу № 29н; введен приказом Минздрава России от 29.04.2026 № 327н)</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Сообщение об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к исполнению обязанностей частного охранника</t>
+          <t>Сообщение об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к осуществлению частной детективной деятельности (выявлено в ходе обязательного предварительного или периодического медицинского осмотра по приказу № 29н)</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Медицинская организация (при выявлении у частного охранника заболеваний, при которых противопоказано исполнять обязанности частного охранника)</t>
+          <t>Медицинская организация, проводившая обязательный предварительный или периодический медицинский осмотр (при выявлении у частного детектива заболеваний, при которых противопоказано осуществлять частную детективную деятельность)</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере частной охранной деятельности; подписание УКЭП медицинским работником и медицинской организацией</t>
+          <t>При выявлении противопоказаний к осуществлению частной детективной деятельности в ходе обязательного предварительного или периодического медицинского осмотра по приказу № 29н: размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере частной детективной деятельности; подписание УКЭП медицинским работником и медицинской организацией (содержание передачи совпадает с п. 16 приказа № 342н; отличие — процедура выявления: медосмотр, а не психиатрическое освидетельствование)</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>п. 16 Порядка прохождения обязательного психиатрического освидетельствования (приложение № 1 к приказу № 342н)</t>
+          <t>п. 14 Порядка прохождения обязательного психиатрического освидетельствования (приложение № 1 к приказу № 342н)</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Сообщение об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к осуществлению частной детективной деятельности</t>
+          <t>Сообщение о наличии оснований для внеочередного медицинского освидетельствования и об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к владению оружием (выявлено в ходе обязательного психиатрического освидетельствования по приказу № 342н)</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Медицинская организация (при выявлении у частного детектива заболеваний, при которых противопоказано осуществлять частную детективную деятельность)</t>
+          <t>Медицинская организация, проводившая обязательное психиатрическое освидетельствование (при выявлении у владельца оружия заболеваний, при которых противопоказано владение оружием)</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере частной детективной деятельности; подписание УКЭП медицинским работником и медицинской организацией</t>
+          <t>При выявлении противопоказаний к владению оружием в ходе обязательного психиатрического освидетельствования по приказу № 342н: размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере оборота оружия; подписание УКЭП медицинским работником и медицинской организацией (содержание передачи совпадает с п. 7.1 приказа № 29н; отличие — процедура выявления: психиатрическое освидетельствование, а не медосмотр)</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1184,42 +1184,42 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Медицинские осмотры с использованием медицинских изделий (дистанционная передача сведений о состоянии здоровья)</t>
+          <t>Обязательное психиатрическое освидетельствование работников</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Постановление Правительства РФ от 30.05.2023 № 866 "Об особенностях проведения медицинских осмотров с использованием медицинских изделий, обеспечивающих автоматизированную дистанционную передачу информации о состоянии здоровья работников и дистанционный контроль состояния их здоровья"</t>
+          <t>Приказ Министерства здравоохранения РФ от 20.05.2022 № 342н "Об утверждении порядка прохождения обязательного психиатрического освидетельствования работниками, осуществляющими отдельные виды деятельности, его периодичности, а также видов деятельности, при осуществлении которых проводится психиатрическое освидетельствование"</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>п. 8 Особенностей проведения медицинских осмотров (приложение к постановлению № 866); п. 3 ч. 3 ст. 91.1 Федерального закона от 21.11.2011 № 323-ФЗ</t>
+          <t>п. 15 Порядка прохождения обязательного психиатрического освидетельствования (приложение № 1 к приказу № 342н)</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Единая государственная информационная система в сфере здравоохранения (ЕГИСЗ)</t>
+          <t>Федеральный реестр документов, содержащий сведения о результатах медицинского освидетельствования (ведется в ЕГИСЗ)</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>сведения о медицинских работниках, проводящих медицинские осмотры с использованием медицинских изделий</t>
+          <t>Сообщение об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к исполнению обязанностей частного охранника (выявлено в ходе обязательного психиатрического освидетельствования по приказу № 342н)</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Медицинская организация / иная организация, имеющая лицензию на медицинскую деятельность (в части медицинских работников, проводящих осмотры с использованием медицинских изделий)</t>
+          <t>Медицинская организация, проводившая обязательное психиатрическое освидетельствование (при выявлении у частного охранника заболеваний, при которых противопоказано исполнять обязанности частного охранника)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Внесение сведений о медицинских работниках в ЕГИСЗ</t>
+          <t>При выявлении противопоказаний к исполнению обязанностей частного охранника в ходе обязательного психиатрического освидетельствования по приказу № 342н: размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере частной охранной деятельности; подписание УКЭП медицинским работником и медицинской организацией (содержание передачи совпадает с п. 7(2) приказа № 29н; отличие — процедура выявления: психиатрическое освидетельствование, а не медосмотр)</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Сведения / запись в ЕГИСЗ</t>
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
         </is>
       </c>
     </row>
@@ -1229,40 +1229,130 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>Обязательное психиатрическое освидетельствование работников</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Приказ Министерства здравоохранения РФ от 20.05.2022 № 342н "Об утверждении порядка прохождения обязательного психиатрического освидетельствования работниками, осуществляющими отдельные виды деятельности, его периодичности, а также видов деятельности, при осуществлении которых проводится психиатрическое освидетельствование"</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>п. 16 Порядка прохождения обязательного психиатрического освидетельствования (приложение № 1 к приказу № 342н)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Федеральный реестр документов, содержащий сведения о результатах медицинского освидетельствования (ведется в ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Сообщение об аннулировании действующего медицинского заключения об отсутствии медицинских противопоказаний к осуществлению частной детективной деятельности (выявлено в ходе обязательного психиатрического освидетельствования по приказу № 342н)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация, проводившая обязательное психиатрическое освидетельствование (при выявлении у частного детектива заболеваний, при которых противопоказано осуществлять частную детективную деятельность)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>При выявлении противопоказаний к осуществлению частной детективной деятельности в ходе обязательного психиатрического освидетельствования по приказу № 342н: размещение сообщения в федеральном реестре документов ЕГИСЗ и передача в федеральный орган исполнительной власти, уполномоченный в сфере частной детективной деятельности; подписание УКЭП медицинским работником и медицинской организацией (содержание передачи совпадает с п. 7(3) приказа № 29н; отличие — процедура выявления: психиатрическое освидетельствование, а не медосмотр)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ, подписанный усиленной квалифицированной электронной подписью</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Медицинские осмотры с использованием медицинских изделий (дистанционная передача сведений о состоянии здоровья)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Постановление Правительства РФ от 30.05.2023 № 866 "Об особенностях проведения медицинских осмотров с использованием медицинских изделий, обеспечивающих автоматизированную дистанционную передачу информации о состоянии здоровья работников и дистанционный контроль состояния их здоровья"</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>п. 8 Особенностей проведения медицинских осмотров (приложение к постановлению № 866); п. 3 ч. 3 ст. 91.1 Федерального закона от 21.11.2011 № 323-ФЗ</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Единая государственная информационная система в сфере здравоохранения (ЕГИСЗ)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>сведения о медицинских работниках, проводящих медицинские осмотры с использованием медицинских изделий</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация / иная организация, имеющая лицензию на медицинскую деятельность (в части медицинских работников, проводящих осмотры с использованием медицинских изделий)</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Внесение сведений о медицинских работниках в ЕГИСЗ</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Сведения / запись в ЕГИСЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Медицинские осмотры с использованием медицинских изделий (дистанционная передача сведений о состоянии здоровья)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 30.05.2023 № 866 "Об особенностях проведения медицинских осмотров с использованием медицинских изделий, обеспечивающих автоматизированную дистанционную передачу информации о состоянии здоровья работников и дистанционный контроль состояния их здоровья"</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>п. 13 подп. "г" Особенностей проведения медицинских осмотров (приложение к постановлению № 866)</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Орган или организация, уполномоченные Министерством транспорта Российской Федерации</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>сведения об оформленных в отношении водителей транспортных средств медицинских заключениях; сведения об условиях применения медицинских изделий</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Медицинская организация (или иная организация, осуществляющая медицинскую деятельность), проводившая медицинский осмотр с использованием медицинских изделий</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Передача сведений в орган (организацию), уполномоченный(ую) Минтрансом России, в соответствии с соглашением об информационном взаимодействии (в целях обеспечения достоверности результатов контроля целостности, актуальности сведений о поверке и условий применения медицинских изделий)</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Сведения / электронная передача (по соглашению об информационном взаимодействии)</t>
         </is>

--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1329,30 +1329,165 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
+          <t>п. 9 Особенностей проведения медицинских осмотров (приложение к постановлению № 866)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>ФГИС «Единая система идентификации и аутентификации» (ЕСИА)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>сведения, необходимые для аутентификации медицинского работника, проводящего медицинский осмотр с использованием медицинских изделий</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Медицинский работник, проводящий медицинский осмотр с использованием медицинских изделий</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Аутентификация в ЕСИА до проведения медицинских осмотров</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Аутентификация в ЕСИА (использование государственной информационной системы)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Медицинские осмотры с использованием медицинских изделий (дистанционная передача сведений о состоянии здоровья)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 30.05.2023 № 866 "Об особенностях проведения медицинских осмотров с использованием медицинских изделий, обеспечивающих автоматизированную дистанционную передачу информации о состоянии здоровья работников и дистанционный контроль состояния их здоровья"</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>п. 10 абз. 1–2 Особенностей проведения медицинских осмотров (приложение к постановлению № 866)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ФГИС «Единая система идентификации и аутентификации» (ЕСИА)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>сведения, необходимые для идентификации личности работника, проходящего медицинский осмотр (при выборе способа идентификации через ЕСИА)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация или работодатель (обеспечение идентификации личности работника)</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Обеспечение идентификации личности работника, исключающей прохождение осмотра иным лицом, в том числе с использованием ЕСИА (альтернативы: медицинские изделия либо ЕБС — см. отдельную строку)</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Идентификация через ЕСИА (использование государственной информационной системы)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Медицинские осмотры с использованием медицинских изделий (дистанционная передача сведений о состоянии здоровья)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 30.05.2023 № 866 "Об особенностях проведения медицинских осмотров с использованием медицинских изделий, обеспечивающих автоматизированную дистанционную передачу информации о состоянии здоровья работников и дистанционный контроль состояния их здоровья"</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>п. 10 абз. 2 Особенностей проведения медицинских осмотров (приложение к постановлению № 866); ст. 10, п. 2 и 3 ч. 1 ст. 15 Федерального закона об идентификации с использованием биометрических персональных данных</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>ГИС «Единая система идентификации и аутентификации физических лиц с использованием биометрических персональных данных» (ЕБС) / единая биометрическая система</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>биометрические персональные данные работника (векторы единой биометрической системы), используемые для аутентификации / идентификации личности при медицинском осмотре</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Медицинская организация или работодатель (обеспечение идентификации личности работника); информационные системы организаций, осуществляющих аутентификацию на основе биометрических персональных данных</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Обеспечение идентификации личности работника с использованием ЕБС / векторов единой биометрической системы (в т.ч. размещенных в единой биометрической системе), исключающей прохождение осмотра иным лицом</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Идентификация / аутентификация с использованием биометрических персональных данных (ЕБС)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Медицинские осмотры с использованием медицинских изделий (дистанционная передача сведений о состоянии здоровья)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 30.05.2023 № 866 "Об особенностях проведения медицинских осмотров с использованием медицинских изделий, обеспечивающих автоматизированную дистанционную передачу информации о состоянии здоровья работников и дистанционный контроль состояния их здоровья"</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
           <t>п. 13 подп. "г" Особенностей проведения медицинских осмотров (приложение к постановлению № 866)</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Орган или организация, уполномоченные Министерством транспорта Российской Федерации</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>сведения об оформленных в отношении водителей транспортных средств медицинских заключениях; сведения об условиях применения медицинских изделий</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Медицинская организация (или иная организация, осуществляющая медицинскую деятельность), проводившая медицинский осмотр с использованием медицинских изделий</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Передача сведений в орган (организацию), уполномоченный(ую) Минтрансом России, в соответствии с соглашением об информационном взаимодействии (в целях обеспечения достоверности результатов контроля целостности, актуальности сведений о поверке и условий применения медицинских изделий)</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Передача сведений в орган (организацию), уполномоченный(ую) Минтрансом России, в соответствии с соглашением об информационном взаимодействии (в целях обеспечения достоверности результатов контроля целостности, актуальности сведений о поверке и условий применения медицинских изделий). Передача тех же сведений работодателю / лицам, указанным в абз. 3 п. 10 (ИП / физлица такси), — для путевых листов, не является передачей в госИС</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Сведения / электронная передача (по соглашению об информационном взаимодействии)</t>
         </is>

--- a/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
+++ b/presentations/Analiz_SUOT_GIS_peredacha_svedeniy.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1493,6 +1493,321 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Обучение по охране труда и проверка знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 24.12.2021 № 2464 "О порядке обучения по охране труда и проверки знания требований охраны труда"</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>п. 78 Правил обучения по охране труда и проверки знания требований охраны труда (приложение к постановлению № 2464)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Единая общероссийская справочно-информационная система по охране труда (ЕИСОТ)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>прохождение проверки знания требований охраны труда (сведения / результаты проверки в рамках использования ЕИСОТ) руководителями и специалистами исполнительных органов субъектов РФ в области охраны труда; руководителями и преподавателями обучающих организаций (ИП), участвующими в работе комиссий по проверке знания; руководителями подразделений по охране труда и специалистами в области охраны труда организаций</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Лица, указанные в п. 78 Правил (руководители и специалисты органов субъектов РФ в области охраны труда; руководители и преподаватели обучающих организаций; руководители служб ОТ и специалисты по охране труда организаций)</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Проверка знания требований охраны труда с использованием ЕИСОТ</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Проверка знания с использованием ЕИСОТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Обучение по охране труда и проверка знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 24.12.2021 № 2464 "О порядке обучения по охране труда и проверки знания требований охраны труда"</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>п. 106, 107, 108 Правил обучения по охране труда и проверки знания требований охраны труда (приложение к постановлению № 2464)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Реестр индивидуальных предпринимателей и юридических лиц, осуществляющих деятельность по обучению своих работников вопросам охраны труда (ведение — Минтруд России; информационная система охраны труда / ЕИСОТ)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>для юридического лица — полное и сокращенное (при наличии) наименование, в том числе фирменное наименование, организационно-правовая форма; адрес места нахождения; ОГРН; данные документа о внесении в ЕГРЮЛ; телефон и адрес электронной почты (при наличии); для индивидуального предпринимателя — ФИО; адрес места жительства; данные документа, удостоверяющего личность; ОГРНИП; данные документа о внесении в ЕГРИП; телефон и адрес электронной почты (при наличии); ИНН; данные документа о постановке на учет в налоговом органе; ОГРН / ОГРНИП; заверенная работодателем копия локального нормативного акта (решения) о проведении обучения по охране труда работодателем без привлечения обучающей организации (с отметкой об учете мнения представительного органа работников — при наличии); адрес официального сайта (при наличии); сведения о среднесписочной численности работников и количестве работников, подлежащих обучению по охране труда; сведения о наличии мест обучения (не менее одного места на 100 работников), оснащенных оборудованием и информационно-справочными системами; сведения о наличии технических средств обучения для отработки практических навыков; сведения о наличии программ обучения по охране труда; сведения о наличии учебно-методических материалов и материалов для проверки знания требований охраны труда; сведения о наличии в штате не менее 2 работников или иных лиц, привлекаемых для проведения обучения; сведения о наличии комиссии по проверке знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Работодатель (индивидуальный предприниматель или юридическое лицо), намеревающийся осуществлять деятельность по обучению своих работников вопросам охраны труда</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Направление (регистрация) уведомления о намерении осуществлять деятельность по обучению своих работников вопросам охраны труда путем заполнения электронной формы в информационной системе охраны труда Минтруда России; подписание электронной подписью; регистрация Минтрудом России в реестре в течение 5 рабочих дней</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ (электронная форма в информационной системе охраны труда), подписанный электронной подписью</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Обучение по охране труда и проверка знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 24.12.2021 № 2464 "О порядке обучения по охране труда и проверки знания требований охраны труда"</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>п. 110 Правил обучения по охране труда и проверки знания требований охраны труда (приложение к постановлению № 2464)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Реестр индивидуальных предпринимателей и юридических лиц, осуществляющих деятельность по обучению своих работников вопросам охраны труда (ведение — Минтруд России; информационная система охраны труда / ЕИСОТ)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>сведения, подлежащие изменению в реестре индивидуальных предпринимателей и юридических лиц, осуществляющих деятельность по обучению своих работников вопросам охраны труда (при необходимости — с приложением копий соответствующих документов)</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Работодатель, сведения о котором содержатся в реестре индивидуальных предпринимателей и юридических лиц, осуществляющих деятельность по обучению своих работников вопросам охраны труда</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Направление в Минтруд России уведомления об изменении сведений в течение 10 рабочих дней со дня наступления изменений; Минтруд России вносит изменения в реестр в течение 5 рабочих дней</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Уведомление об изменении сведений (электронный / документарный обмен с Минтрудом России)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Обучение по охране труда и проверка знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 24.12.2021 № 2464 "О порядке обучения по охране труда и проверки знания требований охраны труда"</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>п. 113 Правил обучения по охране труда и проверки знания требований охраны труда (приложение к постановлению № 2464)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Реестр индивидуальных предпринимателей и юридических лиц, осуществляющих деятельность по обучению своих работников вопросам охраны труда (ведение — Минтруд России; информационная система охраны труда / ЕИСОТ)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>уведомление о прекращении осуществления деятельности в области обучения работников вопросам охраны труда</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель или юридическое лицо, прекращающие деятельность в области обучения работников вопросам охраны труда</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Направление в Минтруд России уведомления о прекращении деятельности; исключение Минтрудом России из реестра в течение 5 рабочих дней</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Уведомление о прекращении деятельности</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Обучение по охране труда и проверка знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 24.12.2021 № 2464 "О порядке обучения по охране труда и проверки знания требований охраны труда"</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>п. 117 Правил обучения по охране труда и проверки знания требований охраны труда (приложение к постановлению № 2464); Правила аккредитации (постановление Правительства РФ от 16.12.2021 № 2334)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Реестр организаций и индивидуальных предпринимателей, оказывающих услуги в области охраны труда (в части обучения по охране труда) (ведение — Минтруд России)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>сведения, предусмотренные Правилами аккредитации организаций, индивидуальных предпринимателей, оказывающих услуги в области охраны труда (постановление № 2334)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Организация / индивидуальный предприниматель, оказывающие (намеренные оказывать) услуги в области охраны труда в части обучения по охране труда (в порядке аккредитации по постановлению № 2334)</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Внесение сведений в реестр организаций и индивидуальных предпринимателей, оказывающих услуги в области охраны труда (в части обучения по охране труда), в соответствии с Правилами аккредитации (постановление № 2334)</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Сведения / запись реестра (в порядке аккредитации по постановлению № 2334)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Обучение по охране труда и проверка знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 24.12.2021 № 2464 "О порядке обучения по охране труда и проверки знания требований охраны труда"</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>п. 118 подп. "а", п. 119 Правил обучения по охране труда и проверки знания требований охраны труда (приложение к постановлению № 2464)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Реестр обученных по охране труда лиц (ведение — Минтруд России; информационная система охраны труда / ЕИСОТ)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>фамилия, имя, отчество (при наличии); СНИЛС; профессия (должность) работника, прошедшего обучение по охране труда; наименование и ИНН организации или индивидуального предпринимателя, направивших работника на обучение; наименование программы обучения по охране труда; результат проверки знания требований охраны труда (удовлетворительно / неудовлетворительно); дата проверки знания требований охраны труда; номер протокола проверки знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Организация или индивидуальный предприниматель, оказывающие услуги по обучению работодателей и работников вопросам охраны труда</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Передача сведений в реестр обученных лиц после проведения проверки знания требований охраны труда путем импортирования электронного документа по форме, установленной Минтрудом России</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ (импорт по форме Минтруда России)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Обучение по охране труда и проверка знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 24.12.2021 № 2464 "О порядке обучения по охране труда и проверки знания требований охраны труда"</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>п. 118 подп. "б", п. 119 Правил обучения по охране труда и проверки знания требований охраны труда (приложение к постановлению № 2464)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Реестр обученных по охране труда лиц (ведение — Минтруд России; информационная система охраны труда / ЕИСОТ)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>фамилия, имя, отчество (при наличии); СНИЛС; профессия (должность) работника, прошедшего обучение по охране труда; наименование программы обучения по охране труда; дата проверки знания требований охраны труда; результат проверки знания требований охраны труда (удовлетворительно / неудовлетворительно); номер протокола проверки знания требований охраны труда</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель или юридическое лицо, осуществляющие деятельность по обучению своих работников вопросам охраны труда</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Передача сведений в реестр обученных лиц после проведения проверки знания требований охраны труда путем импортирования электронного документа по форме, установленной Минтрудом России</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Электронный документ (импорт по форме Минтруда России)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
